--- a/arcb.xlsx
+++ b/arcb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43446476-5497-452C-98B5-2E138AED07E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DF50D95-6F24-4793-9AE2-766202DC72BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{19D556FE-279C-4B40-806E-E8741C3DB8E1}"/>
   </bookViews>
@@ -42,7 +42,7 @@
     <author>Ethan Flynn</author>
   </authors>
   <commentList>
-    <comment ref="V68" authorId="0" shapeId="0" xr:uid="{BDF2B23C-51AD-4F4D-8633-356B93806DDE}">
+    <comment ref="X68" authorId="0" shapeId="0" xr:uid="{BDF2B23C-51AD-4F4D-8633-356B93806DDE}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V77" authorId="0" shapeId="0" xr:uid="{60D31F85-FE87-4D08-9D9B-689E372BA7AF}">
+    <comment ref="X77" authorId="0" shapeId="0" xr:uid="{60D31F85-FE87-4D08-9D9B-689E372BA7AF}">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W77" authorId="0" shapeId="0" xr:uid="{880D4942-D223-4DDB-82AF-7DB9F6D43FF9}">
+    <comment ref="Y77" authorId="0" shapeId="0" xr:uid="{880D4942-D223-4DDB-82AF-7DB9F6D43FF9}">
       <text>
         <r>
           <rPr>
@@ -117,12 +117,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="B79" authorId="0" shapeId="0" xr:uid="{C4189A35-52DD-4921-AC42-41224F68E1BD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Ethan Flynn:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+cic
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="251">
   <si>
     <t>Price</t>
   </si>
@@ -727,9 +752,6 @@
     <t>CFFF</t>
   </si>
   <si>
-    <t>CIC</t>
-  </si>
-  <si>
     <t>Q123</t>
   </si>
   <si>
@@ -868,10 +890,16 @@
     <t>Operating margin</t>
   </si>
   <si>
-    <t>Tax (Benefit)</t>
-  </si>
-  <si>
-    <t>Total term assets</t>
+    <t xml:space="preserve">Tax </t>
+  </si>
+  <si>
+    <t>Other long term assets</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -1043,16 +1071,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>2484</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>65433</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>12009</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>160683</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1067,8 +1095,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17726025" y="57150"/>
-          <a:ext cx="9525" cy="15106650"/>
+          <a:off x="18654919" y="65433"/>
+          <a:ext cx="9525" cy="15103337"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2080,86 +2108,86 @@
     </row>
     <row r="86" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N87" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="88" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N88" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="90" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N90" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N91" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N93" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N94" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N96" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N97" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N99" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="100" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N100" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N102" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="103" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N103" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N105" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N106" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="107" spans="14:14" x14ac:dyDescent="0.25">
@@ -2169,12 +2197,12 @@
     </row>
     <row r="108" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N108" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="109" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N109" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2185,132 +2213,137 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0A573E6-E891-4158-A821-F237648B682F}">
-  <dimension ref="A1:AK79"/>
+  <dimension ref="A1:AM79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="7" width="11.85546875" style="7" customWidth="1"/>
     <col min="8" max="10" width="9.140625" style="7"/>
-    <col min="11" max="12" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="7"/>
-    <col min="14" max="14" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="9.140625" style="7"/>
-    <col min="19" max="20" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="11.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="32" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="10.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.140625" style="7"/>
-    <col min="37" max="37" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="7"/>
+    <col min="17" max="18" width="11.7109375" style="7" customWidth="1"/>
+    <col min="19" max="20" width="9.140625" style="7"/>
+    <col min="21" max="22" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="11.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="30" max="34" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="10.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="9.140625" style="7"/>
+    <col min="39" max="39" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C1" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" t="s">
         <v>239</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>240</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>241</v>
       </c>
-      <c r="F1" t="s">
-        <v>242</v>
-      </c>
       <c r="G1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1" t="s">
         <v>202</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>203</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>204</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>205</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>206</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>207</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>208</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>209</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>210</v>
       </c>
-      <c r="P1" t="s">
-        <v>211</v>
-      </c>
-      <c r="S1">
+      <c r="Q1" t="s">
+        <v>249</v>
+      </c>
+      <c r="R1" t="s">
+        <v>250</v>
+      </c>
+      <c r="U1">
         <v>2020</v>
       </c>
-      <c r="T1">
+      <c r="V1">
         <v>2021</v>
       </c>
-      <c r="U1">
+      <c r="W1">
         <v>2022</v>
       </c>
-      <c r="V1">
+      <c r="X1">
         <v>2023</v>
       </c>
-      <c r="W1">
+      <c r="Y1">
         <v>2024</v>
       </c>
-      <c r="X1">
+      <c r="Z1">
         <v>2025</v>
       </c>
-      <c r="Y1">
+      <c r="AA1">
         <v>2026</v>
       </c>
-      <c r="Z1">
+      <c r="AB1">
         <v>2027</v>
       </c>
-      <c r="AA1">
+      <c r="AC1">
         <v>2028</v>
       </c>
-      <c r="AB1">
+      <c r="AD1">
         <v>2029</v>
       </c>
-      <c r="AC1">
+      <c r="AE1">
         <v>2030</v>
       </c>
-      <c r="AD1">
+      <c r="AF1">
         <v>2031</v>
       </c>
-      <c r="AE1">
+      <c r="AG1">
         <v>2032</v>
       </c>
-      <c r="AF1">
+      <c r="AH1">
         <v>2033</v>
       </c>
-      <c r="AG1">
+      <c r="AI1">
         <v>2034</v>
       </c>
-      <c r="AH1">
+      <c r="AJ1">
         <v>2035</v>
       </c>
     </row>
-    <row r="2" spans="1:37" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:39" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3"/>
       <c r="B3"/>
     </row>
-    <row r="4" spans="1:37" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="B4"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>148</v>
       </c>
@@ -2320,76 +2353,81 @@
       <c r="L6" s="7">
         <v>1077.83</v>
       </c>
+      <c r="M6" s="7">
+        <v>1063.124</v>
+      </c>
       <c r="O6" s="7">
         <v>967.077</v>
       </c>
       <c r="P6" s="7">
         <v>1022.256</v>
       </c>
-      <c r="S6" s="7">
+      <c r="Q6" s="7">
+        <v>1048.1369999999999</v>
+      </c>
+      <c r="U6" s="7">
         <v>2940.163</v>
       </c>
-      <c r="T6" s="7">
+      <c r="V6" s="7">
         <v>3980.067</v>
       </c>
-      <c r="U6" s="7">
+      <c r="W6" s="7">
         <v>5029.0079999999998</v>
       </c>
-      <c r="V6" s="7">
+      <c r="X6" s="7">
         <v>4427.4430000000002</v>
       </c>
-      <c r="W6" s="7">
+      <c r="Y6" s="7">
         <v>4179.0190000000002</v>
       </c>
-      <c r="X6" s="7">
-        <f>+W6*0.95</f>
-        <v>3970.0680499999999</v>
-      </c>
-      <c r="Y6" s="7">
-        <f>+X6*1.11</f>
-        <v>4406.7755354999999</v>
-      </c>
       <c r="Z6" s="7">
-        <f>+Y6*1.02</f>
-        <v>4494.9110462099998</v>
+        <v>4010.1579999999999</v>
       </c>
       <c r="AA6" s="7">
-        <f t="shared" ref="AA6" si="0">+Z6*1.11</f>
-        <v>4989.3512612930999</v>
+        <f>+Z6*1.11</f>
+        <v>4451.27538</v>
       </c>
       <c r="AB6" s="7">
-        <f>+AA6*1.3</f>
-        <v>6486.1566396810304</v>
+        <f>+AA6*1.02</f>
+        <v>4540.3008876000004</v>
       </c>
       <c r="AC6" s="7">
-        <f>+AB6*0.95</f>
-        <v>6161.8488076969788</v>
+        <f t="shared" ref="AC6" si="0">+AB6*1.11</f>
+        <v>5039.733985236001</v>
       </c>
       <c r="AD6" s="7">
-        <f>+AC6*0.95</f>
-        <v>5853.7563673121294</v>
+        <f>+AC6*1.3</f>
+        <v>6551.6541808068014</v>
       </c>
       <c r="AE6" s="7">
-        <f>+AD6*1.2</f>
-        <v>7024.5076407745555</v>
+        <f>+AD6*0.95</f>
+        <v>6224.0714717664614</v>
       </c>
       <c r="AF6" s="7">
         <f>+AE6*0.95</f>
-        <v>6673.2822587358278</v>
+        <v>5912.8678981781377</v>
       </c>
       <c r="AG6" s="7">
-        <f>+AF6*0.95</f>
-        <v>6339.618145799036</v>
+        <f>+AF6*1.2</f>
+        <v>7095.4414778137652</v>
       </c>
       <c r="AH6" s="7">
         <f>+AG6*0.95</f>
-        <v>6022.6372385090835</v>
-      </c>
-      <c r="AJ6" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+        <v>6740.669403923077</v>
+      </c>
+      <c r="AI6" s="7">
+        <f>+AH6*0.95</f>
+        <v>6403.6359337269232</v>
+      </c>
+      <c r="AJ6" s="7">
+        <f>+AI6*0.95</f>
+        <v>6083.4541370405768</v>
+      </c>
+      <c r="AL6" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>149</v>
       </c>
@@ -2399,75 +2437,80 @@
       <c r="L7" s="7">
         <v>1028.9860000000001</v>
       </c>
+      <c r="M7" s="7">
+        <v>928.13099999999997</v>
+      </c>
       <c r="O7" s="7">
         <v>960.447</v>
       </c>
       <c r="P7" s="7">
         <v>984.947</v>
       </c>
-      <c r="U7" s="7">
+      <c r="Q7" s="7">
+        <v>993.51</v>
+      </c>
+      <c r="W7" s="7">
         <v>4634.482</v>
       </c>
-      <c r="V7" s="7">
+      <c r="X7" s="7">
         <v>4254.8239999999996</v>
       </c>
-      <c r="W7" s="7">
+      <c r="Y7" s="7">
         <v>3934.585</v>
       </c>
-      <c r="X7" s="7">
-        <f>+X6*0.95</f>
-        <v>3771.5646474999999</v>
-      </c>
-      <c r="Y7" s="7">
-        <f t="shared" ref="Y7:AH7" si="1">+Y6*0.95</f>
-        <v>4186.4367587249999</v>
-      </c>
       <c r="Z7" s="7">
-        <f t="shared" si="1"/>
-        <v>4270.1654938994998</v>
+        <v>3919.8490000000002</v>
       </c>
       <c r="AA7" s="7">
-        <f t="shared" si="1"/>
-        <v>4739.8836982284447</v>
+        <f t="shared" ref="AA7:AJ7" si="1">+AA6*0.95</f>
+        <v>4228.7116109999997</v>
       </c>
       <c r="AB7" s="7">
         <f t="shared" si="1"/>
-        <v>6161.8488076969788</v>
+        <v>4313.2858432200001</v>
       </c>
       <c r="AC7" s="7">
         <f t="shared" si="1"/>
-        <v>5853.7563673121294</v>
+        <v>4787.7472859742011</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
-        <v>5561.0685489465232</v>
+        <v>6224.0714717664614</v>
       </c>
       <c r="AE7" s="7">
         <f t="shared" si="1"/>
-        <v>6673.2822587358278</v>
+        <v>5912.8678981781377</v>
       </c>
       <c r="AF7" s="7">
         <f t="shared" si="1"/>
-        <v>6339.618145799036</v>
+        <v>5617.2245032692308</v>
       </c>
       <c r="AG7" s="7">
         <f t="shared" si="1"/>
-        <v>6022.6372385090835</v>
+        <v>6740.669403923077</v>
       </c>
       <c r="AH7" s="7">
         <f t="shared" si="1"/>
-        <v>5721.5053765836292</v>
-      </c>
-      <c r="AJ7" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="AK7" s="8">
+        <v>6403.6359337269232</v>
+      </c>
+      <c r="AI7" s="7">
+        <f t="shared" si="1"/>
+        <v>6083.4541370405768</v>
+      </c>
+      <c r="AJ7" s="7">
+        <f t="shared" si="1"/>
+        <v>5779.2814301885473</v>
+      </c>
+      <c r="AL7" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="AM7" s="8">
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K8" s="7">
         <f>+K6-K7</f>
@@ -2477,6 +2520,9 @@
         <f>+L6-L7</f>
         <v>48.843999999999824</v>
       </c>
+      <c r="M8" s="7">
+        <v>134.99299999999999</v>
+      </c>
       <c r="O8" s="7">
         <v>6.63</v>
       </c>
@@ -2484,71 +2530,74 @@
         <f>+P6-P7</f>
         <v>37.308999999999969</v>
       </c>
-      <c r="U8" s="7">
-        <f>+U6-U7</f>
-        <v>394.52599999999984</v>
-      </c>
-      <c r="V8" s="7">
-        <f>+V6-V7</f>
-        <v>172.6190000000006</v>
+      <c r="Q8" s="7">
+        <v>54.627000000000002</v>
       </c>
       <c r="W8" s="7">
         <f>+W6-W7</f>
-        <v>244.4340000000002</v>
+        <v>394.52599999999984</v>
       </c>
       <c r="X8" s="7">
         <f>+X6-X7</f>
-        <v>198.50340249999999</v>
+        <v>172.6190000000006</v>
       </c>
       <c r="Y8" s="7">
-        <f t="shared" ref="Y8:AH8" si="2">+Y6-Y7</f>
-        <v>220.33877677500004</v>
+        <f>+Y6-Y7</f>
+        <v>244.4340000000002</v>
       </c>
       <c r="Z8" s="7">
+        <f>+Z6-Z7</f>
+        <v>90.308999999999742</v>
+      </c>
+      <c r="AA8" s="7">
+        <f t="shared" ref="AA8:AB8" si="2">+AA6-AA7</f>
+        <v>222.56376900000032</v>
+      </c>
+      <c r="AB8" s="7">
         <f t="shared" si="2"/>
-        <v>224.74555231049999</v>
-      </c>
-      <c r="AA8" s="7">
-        <f>AA6*0.1</f>
-        <v>498.93512612930999</v>
-      </c>
-      <c r="AB8" s="7">
-        <f t="shared" ref="AB8:AH8" si="3">AB6*0.1</f>
-        <v>648.61566396810304</v>
+        <v>227.01504438000029</v>
       </c>
       <c r="AC8" s="7">
-        <f t="shared" si="3"/>
-        <v>616.18488076969788</v>
+        <f>AC6*0.1</f>
+        <v>503.97339852360011</v>
       </c>
       <c r="AD8" s="7">
-        <f t="shared" si="3"/>
-        <v>585.37563673121292</v>
+        <f t="shared" ref="AD8:AJ8" si="3">AD6*0.1</f>
+        <v>655.16541808068018</v>
       </c>
       <c r="AE8" s="7">
         <f t="shared" si="3"/>
-        <v>702.45076407745557</v>
+        <v>622.40714717664616</v>
       </c>
       <c r="AF8" s="7">
         <f t="shared" si="3"/>
-        <v>667.32822587358282</v>
+        <v>591.28678981781377</v>
       </c>
       <c r="AG8" s="7">
         <f t="shared" si="3"/>
-        <v>633.9618145799036</v>
+        <v>709.54414778137652</v>
       </c>
       <c r="AH8" s="7">
         <f t="shared" si="3"/>
-        <v>602.26372385090838</v>
-      </c>
-      <c r="AJ8" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="AK8" s="7">
-        <f>NPV(AK7,X12:AH12)</f>
-        <v>2865.3014013020011</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+        <v>674.06694039230774</v>
+      </c>
+      <c r="AI8" s="7">
+        <f t="shared" si="3"/>
+        <v>640.36359337269232</v>
+      </c>
+      <c r="AJ8" s="7">
+        <f t="shared" si="3"/>
+        <v>608.34541370405771</v>
+      </c>
+      <c r="AL8" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="AM8" s="7">
+        <f>NPV(AM7,Z12:AJ12)</f>
+        <v>2843.4543787758871</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>150</v>
       </c>
@@ -2558,30 +2607,29 @@
       <c r="L9" s="7">
         <v>0.38200000000000001</v>
       </c>
+      <c r="M9" s="7">
+        <v>1.7110000000000001</v>
+      </c>
       <c r="O9" s="7">
         <v>-2.456</v>
       </c>
       <c r="P9" s="7">
         <v>-1.341</v>
       </c>
-      <c r="U9" s="7">
+      <c r="Q9" s="7">
+        <v>-1.119</v>
+      </c>
+      <c r="W9" s="7">
         <v>-6.2229999999999999</v>
       </c>
-      <c r="V9" s="7">
+      <c r="X9" s="7">
         <v>14.295999999999999</v>
       </c>
-      <c r="W9" s="7">
+      <c r="Y9" s="7">
         <v>-25.72</v>
       </c>
-      <c r="X9" s="7">
-        <f>AVERAGE(U9:W9)</f>
-        <v>-5.8823333333333325</v>
-      </c>
-      <c r="Y9" s="7">
-        <v>-5.8819999999999997</v>
-      </c>
       <c r="Z9" s="7">
-        <v>-5.8819999999999997</v>
+        <v>-7.2140000000000004</v>
       </c>
       <c r="AA9" s="7">
         <v>-5.8819999999999997</v>
@@ -2607,15 +2655,21 @@
       <c r="AH9" s="7">
         <v>-5.8819999999999997</v>
       </c>
-      <c r="AJ9" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="AK9" s="7">
-        <f>+AK8/AH14</f>
-        <v>116.22526269833291</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AI9" s="7">
+        <v>-5.8819999999999997</v>
+      </c>
+      <c r="AJ9" s="7">
+        <v>-5.8819999999999997</v>
+      </c>
+      <c r="AL9" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="AM9" s="7">
+        <f>+AM8/AJ14</f>
+        <v>115.33908160369478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>151</v>
       </c>
@@ -2627,6 +2681,9 @@
         <f>+L8+L9</f>
         <v>49.225999999999821</v>
       </c>
+      <c r="M10" s="7">
+        <v>136.70400000000001</v>
+      </c>
       <c r="O10" s="7">
         <f>+O8+O9</f>
         <v>4.1739999999999995</v>
@@ -2635,66 +2692,69 @@
         <f>+P8+P9</f>
         <v>35.967999999999968</v>
       </c>
-      <c r="U10" s="7">
-        <f>+U8+U9</f>
-        <v>388.30299999999983</v>
-      </c>
-      <c r="V10" s="7">
-        <f>+V8+V9</f>
-        <v>186.91500000000059</v>
+      <c r="Q10" s="7">
+        <v>53.508000000000003</v>
       </c>
       <c r="W10" s="7">
         <f>+W8+W9</f>
+        <v>388.30299999999983</v>
+      </c>
+      <c r="X10" s="7">
+        <f>+X8+X9</f>
+        <v>186.91500000000059</v>
+      </c>
+      <c r="Y10" s="7">
+        <f>+Y8+Y9</f>
         <v>218.7140000000002</v>
       </c>
-      <c r="X10" s="7">
-        <f t="shared" ref="X10:AH10" si="4">+X8+X9</f>
-        <v>192.62106916666667</v>
-      </c>
-      <c r="Y10" s="7">
-        <f t="shared" si="4"/>
-        <v>214.45677677500004</v>
-      </c>
       <c r="Z10" s="7">
-        <f t="shared" si="4"/>
-        <v>218.86355231049998</v>
+        <f t="shared" ref="Z10:AJ10" si="4">+Z8+Z9</f>
+        <v>83.094999999999743</v>
       </c>
       <c r="AA10" s="7">
         <f t="shared" si="4"/>
-        <v>493.05312612930999</v>
+        <v>216.68176900000032</v>
       </c>
       <c r="AB10" s="7">
         <f t="shared" si="4"/>
-        <v>642.73366396810309</v>
+        <v>221.13304438000029</v>
       </c>
       <c r="AC10" s="7">
         <f t="shared" si="4"/>
-        <v>610.30288076969794</v>
+        <v>498.09139852360011</v>
       </c>
       <c r="AD10" s="7">
         <f t="shared" si="4"/>
-        <v>579.49363673121297</v>
+        <v>649.28341808068024</v>
       </c>
       <c r="AE10" s="7">
         <f t="shared" si="4"/>
-        <v>696.56876407745563</v>
+        <v>616.52514717664621</v>
       </c>
       <c r="AF10" s="7">
         <f t="shared" si="4"/>
-        <v>661.44622587358288</v>
+        <v>585.40478981781382</v>
       </c>
       <c r="AG10" s="7">
         <f t="shared" si="4"/>
-        <v>628.07981457990365</v>
+        <v>703.66214778137658</v>
       </c>
       <c r="AH10" s="7">
         <f t="shared" si="4"/>
-        <v>596.38172385090843</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+        <v>668.18494039230779</v>
+      </c>
+      <c r="AI10" s="7">
+        <f t="shared" si="4"/>
+        <v>634.48159337269237</v>
+      </c>
+      <c r="AJ10" s="7">
+        <f t="shared" si="4"/>
+        <v>602.46341370405776</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K11" s="7">
         <v>1.7649999999999999</v>
@@ -2702,67 +2762,72 @@
       <c r="L11" s="7">
         <v>-2.3029999999999999</v>
       </c>
+      <c r="M11" s="7">
+        <v>36.39</v>
+      </c>
       <c r="O11" s="7">
         <v>1.0429999999999999</v>
       </c>
       <c r="P11" s="7">
         <v>-10.159000000000001</v>
       </c>
-      <c r="U11" s="7">
+      <c r="Q11" s="7">
+        <v>-14.234</v>
+      </c>
+      <c r="W11" s="7">
         <v>-93.655000000000001</v>
       </c>
-      <c r="V11" s="7">
+      <c r="X11" s="7">
         <v>-44.750999999999998</v>
       </c>
-      <c r="W11" s="7">
+      <c r="Y11" s="7">
         <v>-45.353000000000002</v>
       </c>
-      <c r="X11" s="7">
-        <f>-0.02*X6</f>
-        <v>-79.401360999999994</v>
-      </c>
-      <c r="Y11" s="7">
-        <f t="shared" ref="Y11:AH11" si="5">-0.02*Y6</f>
-        <v>-88.135510710000005</v>
-      </c>
       <c r="Z11" s="7">
-        <f t="shared" si="5"/>
-        <v>-89.898220924200004</v>
+        <v>-22.997</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" si="5"/>
-        <v>-99.787025225861996</v>
+        <f t="shared" ref="AA11:AJ11" si="5">-0.02*AA6</f>
+        <v>-89.025507599999997</v>
       </c>
       <c r="AB11" s="7">
         <f t="shared" si="5"/>
-        <v>-129.72313279362061</v>
+        <v>-90.806017752000002</v>
       </c>
       <c r="AC11" s="7">
         <f t="shared" si="5"/>
-        <v>-123.23697615393958</v>
+        <v>-100.79467970472002</v>
       </c>
       <c r="AD11" s="7">
         <f t="shared" si="5"/>
-        <v>-117.0751273462426</v>
+        <v>-131.03308361613603</v>
       </c>
       <c r="AE11" s="7">
         <f t="shared" si="5"/>
-        <v>-140.49015281549111</v>
+        <v>-124.48142943532923</v>
       </c>
       <c r="AF11" s="7">
         <f t="shared" si="5"/>
-        <v>-133.46564517471657</v>
+        <v>-118.25735796356275</v>
       </c>
       <c r="AG11" s="7">
         <f t="shared" si="5"/>
-        <v>-126.79236291598072</v>
+        <v>-141.90882955627532</v>
       </c>
       <c r="AH11" s="7">
         <f t="shared" si="5"/>
-        <v>-120.45274477018167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+        <v>-134.81338807846154</v>
+      </c>
+      <c r="AI11" s="7">
+        <f t="shared" si="5"/>
+        <v>-128.07271867453846</v>
+      </c>
+      <c r="AJ11" s="7">
+        <f t="shared" si="5"/>
+        <v>-121.66908274081153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>152</v>
       </c>
@@ -2774,6 +2839,10 @@
         <f>+L10+L11</f>
         <v>46.922999999999824</v>
       </c>
+      <c r="M12" s="7">
+        <f>+M10-M11</f>
+        <v>100.31400000000001</v>
+      </c>
       <c r="O12" s="7">
         <f>+O10-O11</f>
         <v>3.1309999999999993</v>
@@ -2782,64 +2851,68 @@
         <f>+P10+P11</f>
         <v>25.808999999999969</v>
       </c>
-      <c r="U12" s="7">
-        <f>+U10+U11</f>
-        <v>294.6479999999998</v>
-      </c>
-      <c r="V12" s="7">
-        <f>+V10+V11</f>
-        <v>142.16400000000058</v>
+      <c r="Q12" s="7">
+        <f>+Q10+Q11</f>
+        <v>39.274000000000001</v>
       </c>
       <c r="W12" s="7">
         <f>+W10+W11</f>
-        <v>173.36100000000019</v>
+        <v>294.6479999999998</v>
       </c>
       <c r="X12" s="7">
         <f>+X10+X11</f>
-        <v>113.21970816666668</v>
+        <v>142.16400000000058</v>
       </c>
       <c r="Y12" s="7">
-        <f t="shared" ref="Y12:AH12" si="6">+Y10+Y11</f>
-        <v>126.32126606500003</v>
+        <f>+Y10+Y11</f>
+        <v>173.36100000000019</v>
       </c>
       <c r="Z12" s="7">
-        <f t="shared" si="6"/>
-        <v>128.96533138629997</v>
+        <f>+Z10+Z11</f>
+        <v>60.097999999999743</v>
       </c>
       <c r="AA12" s="7">
-        <f t="shared" si="6"/>
-        <v>393.26610090344798</v>
+        <f t="shared" ref="AA12:AJ12" si="6">+AA10+AA11</f>
+        <v>127.65626140000032</v>
       </c>
       <c r="AB12" s="7">
         <f t="shared" si="6"/>
-        <v>513.01053117448248</v>
+        <v>130.32702662800028</v>
       </c>
       <c r="AC12" s="7">
         <f t="shared" si="6"/>
-        <v>487.06590461575837</v>
+        <v>397.29671881888009</v>
       </c>
       <c r="AD12" s="7">
         <f t="shared" si="6"/>
-        <v>462.41850938497038</v>
+        <v>518.25033446454427</v>
       </c>
       <c r="AE12" s="7">
         <f t="shared" si="6"/>
-        <v>556.07861126196451</v>
+        <v>492.04371774131698</v>
       </c>
       <c r="AF12" s="7">
         <f t="shared" si="6"/>
-        <v>527.98058069886633</v>
+        <v>467.14743185425107</v>
       </c>
       <c r="AG12" s="7">
         <f t="shared" si="6"/>
-        <v>501.28745166392292</v>
+        <v>561.75331822510122</v>
       </c>
       <c r="AH12" s="7">
         <f t="shared" si="6"/>
-        <v>475.92897908072678</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+        <v>533.37155231384622</v>
+      </c>
+      <c r="AI12" s="7">
+        <f t="shared" si="6"/>
+        <v>506.40887469815391</v>
+      </c>
+      <c r="AJ12" s="7">
+        <f t="shared" si="6"/>
+        <v>480.79433096324624</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>153</v>
       </c>
@@ -2851,6 +2924,10 @@
         <f>+L12/L14</f>
         <v>1.9616956177342764</v>
       </c>
+      <c r="M13" s="7">
+        <f>+M12/M14</f>
+        <v>4.2344234642965084</v>
+      </c>
       <c r="O13" s="7">
         <f>+O12/O14</f>
         <v>0.13453493237546407</v>
@@ -2859,64 +2936,68 @@
         <f>+P12/P14</f>
         <v>1.1217057959841015</v>
       </c>
-      <c r="U13" s="7">
-        <f t="shared" ref="U13:AH13" si="7">+U12/U14</f>
+      <c r="Q13" s="7">
+        <f>+Q12/Q14</f>
+        <v>1.7216626402188004</v>
+      </c>
+      <c r="W13" s="7">
+        <f t="shared" ref="W13:AJ13" si="7">+W12/W14</f>
         <v>11.552781178919421</v>
       </c>
-      <c r="V13" s="7">
+      <c r="X13" s="7">
         <f t="shared" si="7"/>
         <v>5.7709036028447525</v>
       </c>
-      <c r="W13" s="7">
+      <c r="Y13" s="7">
         <f t="shared" si="7"/>
         <v>7.2779062286486225</v>
       </c>
-      <c r="X13" s="7">
-        <f t="shared" si="7"/>
-        <v>4.592514051647326</v>
-      </c>
-      <c r="Y13" s="7">
-        <f t="shared" si="7"/>
-        <v>5.1239713651482592</v>
-      </c>
       <c r="Z13" s="7">
         <f t="shared" si="7"/>
-        <v>5.2312226254938539</v>
+        <v>2.6315603951605415</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="7"/>
-        <v>15.952058609639719</v>
+        <v>5.1781228004705442</v>
       </c>
       <c r="AB13" s="7">
         <f t="shared" si="7"/>
-        <v>20.809253688171115</v>
+        <v>5.2864570895225853</v>
       </c>
       <c r="AC13" s="7">
         <f t="shared" si="7"/>
-        <v>19.756861421155982</v>
+        <v>16.115552623164731</v>
       </c>
       <c r="AD13" s="7">
         <f t="shared" si="7"/>
-        <v>18.757088767491599</v>
+        <v>21.021795905753631</v>
       </c>
       <c r="AE13" s="7">
         <f t="shared" si="7"/>
-        <v>22.556224851416239</v>
+        <v>19.958776527859367</v>
       </c>
       <c r="AF13" s="7">
         <f t="shared" si="7"/>
-        <v>21.416484026238848</v>
+        <v>18.948908118859819</v>
       </c>
       <c r="AG13" s="7">
         <f t="shared" si="7"/>
-        <v>20.333730242320325</v>
+        <v>22.786408073058098</v>
       </c>
       <c r="AH13" s="7">
         <f t="shared" si="7"/>
-        <v>19.305114147597727</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+        <v>21.635158086798615</v>
+      </c>
+      <c r="AI13" s="7">
+        <f t="shared" si="7"/>
+        <v>20.541470599852104</v>
+      </c>
+      <c r="AJ13" s="7">
+        <f t="shared" si="7"/>
+        <v>19.502467487252922</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>154</v>
       </c>
@@ -2926,30 +3007,29 @@
       <c r="L14" s="7">
         <v>23.919612999999998</v>
       </c>
+      <c r="M14" s="7">
+        <v>23.69012</v>
+      </c>
       <c r="O14" s="7">
         <v>23.272766000000001</v>
       </c>
       <c r="P14" s="7">
         <v>23.008707000000001</v>
       </c>
-      <c r="U14" s="7">
+      <c r="Q14" s="7">
+        <v>22.811669999999999</v>
+      </c>
+      <c r="W14" s="7">
         <v>25.504508000000001</v>
       </c>
-      <c r="V14" s="7">
+      <c r="X14" s="7">
         <v>24.634616999999999</v>
       </c>
-      <c r="W14" s="7">
+      <c r="Y14" s="7">
         <v>23.820174999999999</v>
       </c>
-      <c r="X14" s="7">
-        <f>AVERAGE(U14:W14)</f>
-        <v>24.653099999999998</v>
-      </c>
-      <c r="Y14" s="7">
-        <v>24.652999999999999</v>
-      </c>
       <c r="Z14" s="7">
-        <v>24.652999999999999</v>
+        <v>22.837401</v>
       </c>
       <c r="AA14" s="7">
         <v>24.652999999999999</v>
@@ -2975,11 +3055,17 @@
       <c r="AH14" s="7">
         <v>24.652999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:37" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI14" s="7">
+        <v>24.652999999999999</v>
+      </c>
+      <c r="AJ14" s="7">
+        <v>24.652999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K16" s="8">
         <f>+K8/K6</f>
@@ -2989,6 +3075,10 @@
         <f>+L8/L6</f>
         <v>4.5316979486560799E-2</v>
       </c>
+      <c r="M16" s="8">
+        <f>+M8/M6</f>
+        <v>0.12697766206011715</v>
+      </c>
       <c r="O16" s="8">
         <f>+O8/O6</f>
         <v>6.8557105587248998E-3</v>
@@ -2997,23 +3087,31 @@
         <f>+P8/P6</f>
         <v>3.6496728803743848E-2</v>
       </c>
-      <c r="U16" s="8">
-        <f>+U8/U6</f>
-        <v>7.8450064108070594E-2</v>
-      </c>
-      <c r="V16" s="8">
-        <f>+V8/V6</f>
-        <v>3.8988418371507121E-2</v>
+      <c r="Q16" s="8">
+        <f>+Q8/Q6</f>
+        <v>5.2118186840079114E-2</v>
       </c>
       <c r="W16" s="8">
         <f>+W8/W6</f>
+        <v>7.8450064108070594E-2</v>
+      </c>
+      <c r="X16" s="8">
+        <f>+X8/X6</f>
+        <v>3.8988418371507121E-2</v>
+      </c>
+      <c r="Y16" s="8">
+        <f>+Y8/Y6</f>
         <v>5.8490760630664801E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:34" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z16" s="8">
+        <f>+Z8/Z6</f>
+        <v>2.2520060306850689E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O17" s="8">
         <f>+(O6-L6)/L6</f>
@@ -3023,57 +3121,62 @@
         <f>+(P6-L6)/L6</f>
         <v>-5.1561006837812978E-2</v>
       </c>
-      <c r="T17" s="8">
-        <f>SUM(T6-S6)/S6</f>
-        <v>0.35368923423633314</v>
-      </c>
-      <c r="U17" s="8">
-        <f>SUM(U6-T6)/T6</f>
-        <v>0.26354857845357876</v>
+      <c r="Q17" s="8">
+        <f>+(Q6-M6)/M6</f>
+        <v>-1.4097132601653316E-2</v>
       </c>
       <c r="V17" s="8">
         <f>SUM(V6-U6)/U6</f>
-        <v>-0.11961901830341086</v>
+        <v>0.35368923423633314</v>
       </c>
       <c r="W17" s="8">
         <f>SUM(W6-V6)/V6</f>
+        <v>0.26354857845357876</v>
+      </c>
+      <c r="X17" s="8">
+        <f>SUM(X6-W6)/W6</f>
+        <v>-0.11961901830341086</v>
+      </c>
+      <c r="Y17" s="8">
+        <f>SUM(Y6-X6)/X6</f>
         <v>-5.6110039135455828E-2</v>
       </c>
-      <c r="X17" s="8">
-        <v>-0.05</v>
-      </c>
-      <c r="Y17" s="8">
-        <v>0.11</v>
-      </c>
       <c r="Z17" s="8">
-        <v>0.2</v>
+        <f>SUM(Z6-Y6)/Y6</f>
+        <v>-4.0406851464422709E-2</v>
       </c>
       <c r="AA17" s="8">
         <v>0.11</v>
       </c>
       <c r="AB17" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="AC17" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="AD17" s="8">
         <v>0.3</v>
       </c>
-      <c r="AC17" s="8">
+      <c r="AE17" s="8">
         <v>-0.05</v>
       </c>
-      <c r="AD17" s="8">
+      <c r="AF17" s="8">
         <v>-0.05</v>
       </c>
-      <c r="AE17" s="8">
+      <c r="AG17" s="8">
         <v>0.6</v>
       </c>
-      <c r="AF17" s="8">
+      <c r="AH17" s="8">
         <v>0.2</v>
       </c>
-      <c r="AG17" s="8">
+      <c r="AI17" s="8">
         <v>-0.05</v>
       </c>
-      <c r="AH17" s="8">
+      <c r="AJ17" s="8">
         <v>-0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>155</v>
       </c>
@@ -3093,20 +3196,24 @@
         <f>114.874+24.801</f>
         <v>139.67499999999998</v>
       </c>
-      <c r="U19" s="7">
+      <c r="W19" s="7">
         <f>158.372+167.662</f>
         <v>326.03399999999999</v>
       </c>
-      <c r="V19" s="7">
+      <c r="X19" s="7">
         <f>262.226+67.842</f>
         <v>330.06799999999998</v>
       </c>
-      <c r="W19" s="7">
+      <c r="Y19" s="7">
         <f>127.444+29.759</f>
         <v>157.203</v>
       </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z19" s="7">
+        <f>102.03+22.204</f>
+        <v>124.23400000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>156</v>
       </c>
@@ -3126,22 +3233,26 @@
         <f>77.549+163.85</f>
         <v>241.399</v>
       </c>
-      <c r="U20" s="7">
+      <c r="W20" s="7">
         <f>198.371+66.252</f>
         <v>264.62299999999999</v>
       </c>
-      <c r="V20" s="7">
+      <c r="X20" s="7">
         <f>66.948+161.99</f>
         <v>228.93799999999999</v>
       </c>
-      <c r="W20" s="7">
+      <c r="Y20" s="7">
         <f>63.978+125.156</f>
         <v>189.13400000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z20" s="7">
+        <f>135.974+ 87.882</f>
+        <v>223.85599999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K21" s="7">
         <f>+K19-K20</f>
@@ -3159,24 +3270,24 @@
         <f>+P19-P20</f>
         <v>-101.72400000000002</v>
       </c>
-      <c r="U21" s="7">
-        <f>+U19-U20</f>
-        <v>61.411000000000001</v>
-      </c>
-      <c r="V21" s="7">
-        <f>+V19-V20</f>
-        <v>101.13</v>
-      </c>
       <c r="W21" s="7">
         <f>+W19-W20</f>
+        <v>61.411000000000001</v>
+      </c>
+      <c r="X21" s="7">
+        <f>+X19-X20</f>
+        <v>101.13</v>
+      </c>
+      <c r="Y21" s="7">
+        <f>+Y19-Y20</f>
         <v>-31.931000000000012</v>
       </c>
-      <c r="AA21" s="7">
-        <f>+AA8/AA6</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z21" s="7">
+        <f>+Z19-Z20</f>
+        <v>-99.621999999999986</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>157</v>
       </c>
@@ -3192,17 +3303,20 @@
       <c r="P23" s="7">
         <v>536.79100000000005</v>
       </c>
-      <c r="U23" s="7">
+      <c r="W23" s="7">
         <v>406.62</v>
       </c>
-      <c r="V23" s="7">
+      <c r="X23" s="7">
         <v>46.067999999999998</v>
       </c>
-      <c r="W23" s="7">
+      <c r="Y23" s="7">
         <v>520.11900000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z23" s="7">
+        <v>566.07100000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>158</v>
       </c>
@@ -3218,17 +3332,20 @@
       <c r="P24" s="7">
         <v>1200.2190000000001</v>
       </c>
-      <c r="U24" s="7">
+      <c r="W24" s="7">
         <v>1038.8320000000001</v>
       </c>
-      <c r="V24" s="7">
+      <c r="X24" s="7">
         <v>1126.0550000000001</v>
       </c>
-      <c r="W24" s="7">
+      <c r="Y24" s="7">
         <v>1166.1610000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z24" s="7">
+        <v>1201.383</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>159</v>
       </c>
@@ -3244,17 +3361,20 @@
       <c r="P25" s="7">
         <v>356.31900000000002</v>
       </c>
-      <c r="U25" s="7">
+      <c r="W25" s="7">
         <v>302.89100000000002</v>
       </c>
-      <c r="V25" s="7">
+      <c r="X25" s="7">
         <v>319.46600000000001</v>
       </c>
-      <c r="W25" s="7">
+      <c r="Y25" s="7">
         <v>351.90699999999998</v>
       </c>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z25" s="7">
+        <v>363.34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>160</v>
       </c>
@@ -3270,17 +3390,20 @@
       <c r="P26" s="7">
         <v>183.52</v>
       </c>
-      <c r="U26" s="7">
+      <c r="W26" s="7">
         <v>180.929</v>
       </c>
-      <c r="V26" s="7">
+      <c r="X26" s="7">
         <v>173.35400000000001</v>
       </c>
-      <c r="W26" s="7">
+      <c r="Y26" s="7">
         <v>182.39599999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z26" s="7">
+        <v>190.673</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>161</v>
       </c>
@@ -3296,19 +3419,22 @@
       <c r="P27" s="7">
         <v>35.064999999999998</v>
       </c>
-      <c r="U27" s="7">
+      <c r="W27" s="7">
         <v>23.466000000000001</v>
       </c>
-      <c r="V27" s="7">
+      <c r="X27" s="7">
         <v>24.428999999999998</v>
       </c>
-      <c r="W27" s="7">
+      <c r="Y27" s="7">
         <v>32.262999999999998</v>
       </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z27" s="7">
+        <v>41.530999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K28" s="7">
         <v>1199.18</v>
@@ -3322,17 +3448,20 @@
       <c r="P28" s="7">
         <v>1198.7570000000001</v>
       </c>
-      <c r="U28" s="7">
+      <c r="W28" s="7">
         <v>1142.2180000000001</v>
       </c>
-      <c r="V28" s="7">
+      <c r="X28" s="7">
         <v>1188.548</v>
       </c>
-      <c r="W28" s="7">
+      <c r="Y28" s="7">
         <v>1186.8</v>
       </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z28" s="7">
+        <v>1219.5640000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>162</v>
       </c>
@@ -3350,20 +3479,23 @@
         <f>+P23+P24+P25+P26+P27-P28</f>
         <v>1113.1570000000002</v>
       </c>
-      <c r="U29" s="7">
-        <f>SUM(U23:U27)-U28</f>
+      <c r="W29" s="7">
+        <f>SUM(W23:W27)-W28</f>
         <v>810.52000000000021</v>
       </c>
-      <c r="V29" s="7">
-        <f>+V23+V24+V25+V26+V27-V28</f>
+      <c r="X29" s="7">
+        <f>+X23+X24+X25+X26+X27-X28</f>
         <v>500.82400000000007</v>
       </c>
-      <c r="W29" s="7">
-        <f>+W23+W24+W25+W26+W27-W28</f>
+      <c r="Y29" s="7">
+        <f>+Y23+Y24+Y25+Y26+Y27-Y28</f>
         <v>1066.046</v>
       </c>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z29" s="7">
+        <v>1143.4369999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>163</v>
       </c>
@@ -3379,17 +3511,20 @@
       <c r="P30" s="7">
         <v>304.75299999999999</v>
       </c>
-      <c r="U30" s="7">
+      <c r="W30" s="7">
         <v>305.38200000000001</v>
       </c>
-      <c r="V30" s="7">
+      <c r="X30" s="7">
         <v>304.75299999999999</v>
       </c>
-      <c r="W30" s="7">
+      <c r="Y30" s="7">
         <v>304.75299999999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z30" s="7">
+        <v>304.75299999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>164</v>
       </c>
@@ -3405,17 +3540,20 @@
       <c r="P31" s="7">
         <v>82.448999999999998</v>
       </c>
-      <c r="U31" s="7">
+      <c r="W31" s="7">
         <v>113.79600000000001</v>
       </c>
-      <c r="V31" s="7">
+      <c r="X31" s="7">
         <v>101.15</v>
       </c>
-      <c r="W31" s="7">
+      <c r="Y31" s="7">
         <v>88.614999999999995</v>
       </c>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Z31" s="7">
+        <v>69.391000000000005</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>165</v>
       </c>
@@ -3431,19 +3569,22 @@
       <c r="P32" s="7">
         <v>229.905</v>
       </c>
-      <c r="U32" s="7">
+      <c r="W32" s="7">
         <v>166.51499999999999</v>
       </c>
-      <c r="V32" s="7">
+      <c r="X32" s="7">
         <v>169.999</v>
       </c>
-      <c r="W32" s="7">
+      <c r="Y32" s="7">
         <v>192.75299999999999</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z32" s="7">
+        <v>220.15700000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K33" s="7">
         <v>2406.884</v>
@@ -3457,17 +3598,20 @@
       <c r="P33" s="7">
         <v>2467.4360000000001</v>
       </c>
-      <c r="U33" s="7">
+      <c r="W33" s="7">
         <v>101.94799999999999</v>
       </c>
-      <c r="V33" s="7">
+      <c r="X33" s="7">
         <v>101.44499999999999</v>
       </c>
-      <c r="W33" s="7">
+      <c r="Y33" s="7">
         <v>92.385999999999996</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z33" s="7">
+        <v>79.558000000000007</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>166</v>
       </c>
@@ -3483,17 +3627,20 @@
       <c r="P35" s="7">
         <v>176.90299999999999</v>
       </c>
-      <c r="U35" s="7">
+      <c r="W35" s="7">
         <v>317.541</v>
       </c>
-      <c r="V35" s="7">
+      <c r="X35" s="7">
         <v>214.00399999999999</v>
       </c>
-      <c r="W35" s="7">
+      <c r="Y35" s="7">
         <v>172.76300000000001</v>
       </c>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z35" s="7">
+        <v>154.48699999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>167</v>
       </c>
@@ -3506,17 +3653,14 @@
       <c r="P36" s="7">
         <v>3.63</v>
       </c>
-      <c r="U36" s="7">
+      <c r="W36" s="7">
         <v>16.63</v>
       </c>
-      <c r="V36" s="7">
+      <c r="X36" s="7">
         <v>10.41</v>
       </c>
-      <c r="W36" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>168</v>
       </c>
@@ -3532,17 +3676,20 @@
       <c r="P37" s="7">
         <v>368.62299999999999</v>
       </c>
-      <c r="U37" s="7">
+      <c r="W37" s="7">
         <v>341.822</v>
       </c>
-      <c r="V37" s="7">
+      <c r="X37" s="7">
         <v>378.029</v>
       </c>
-      <c r="W37" s="7">
+      <c r="Y37" s="7">
         <v>394.88</v>
       </c>
-    </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z37" s="7">
+        <v>378.125</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>169</v>
       </c>
@@ -3560,20 +3707,23 @@
         <f>34.967+215.376</f>
         <v>250.34300000000002</v>
       </c>
-      <c r="U38" s="7">
+      <c r="W38" s="7">
         <f>26.225+147.828</f>
         <v>174.053</v>
       </c>
-      <c r="V38" s="7">
+      <c r="X38" s="7">
         <f>32.172+176.621</f>
         <v>208.79300000000001</v>
       </c>
-      <c r="W38" s="7">
+      <c r="Y38" s="7">
         <f>34.364+189.978</f>
         <v>224.34200000000001</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z38" s="7">
+        <v>36.393999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>170</v>
       </c>
@@ -3589,17 +3739,20 @@
       <c r="P39" s="7">
         <v>78.278999999999996</v>
       </c>
-      <c r="U39" s="7">
+      <c r="W39" s="7">
         <v>61.274999999999999</v>
       </c>
-      <c r="V39" s="7">
+      <c r="X39" s="7">
         <v>55.784999999999997</v>
       </c>
-      <c r="W39" s="7">
+      <c r="Y39" s="7">
         <v>78.649000000000001</v>
       </c>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z39" s="7">
+        <v>111.58</v>
+      </c>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>171</v>
       </c>
@@ -3615,17 +3768,20 @@
       <c r="P40" s="7">
         <v>34.722999999999999</v>
       </c>
-      <c r="U40" s="7">
+      <c r="W40" s="7">
         <v>154.745</v>
       </c>
-      <c r="V40" s="7">
+      <c r="X40" s="7">
         <v>40.552999999999997</v>
       </c>
-      <c r="W40" s="7">
+      <c r="Y40" s="7">
         <v>39.590000000000003</v>
       </c>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z40" s="7">
+        <v>34.47</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>173</v>
       </c>
@@ -3645,20 +3801,24 @@
         <f>+P43-P42</f>
         <v>1167.0100000000002</v>
       </c>
-      <c r="U41" s="7">
-        <f>SUM(U35:U40)</f>
-        <v>1066.0659999999998</v>
-      </c>
-      <c r="V41" s="7">
-        <f>SUM(V35:V40)</f>
-        <v>907.57399999999996</v>
-      </c>
       <c r="W41" s="7">
         <f>SUM(W35:W40)</f>
+        <v>1066.0659999999998</v>
+      </c>
+      <c r="X41" s="7">
+        <f>SUM(X35:X40)</f>
+        <v>907.57399999999996</v>
+      </c>
+      <c r="Y41" s="7">
+        <f>SUM(Y35:Y40)</f>
         <v>910.22400000000005</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z41" s="7">
+        <f>SUM(Z35:Z40)</f>
+        <v>715.05600000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>172</v>
       </c>
@@ -3674,17 +3834,20 @@
       <c r="P42" s="7">
         <v>1300.4259999999999</v>
       </c>
-      <c r="U42" s="7">
+      <c r="W42" s="7">
         <v>1151.4010000000001</v>
       </c>
-      <c r="V42" s="7">
+      <c r="X42" s="7">
         <v>1242.3630000000001</v>
       </c>
-      <c r="W42" s="7">
+      <c r="Y42" s="7">
         <v>1314.3620000000001</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z42" s="7">
+        <v>1295.721</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>174</v>
       </c>
@@ -3700,18 +3863,21 @@
       <c r="P43" s="7">
         <v>2467.4360000000001</v>
       </c>
-      <c r="U43" s="7">
-        <f>+U41+U42</f>
+      <c r="W43" s="7">
+        <f>+W41+W42</f>
         <v>2217.4669999999996</v>
       </c>
-      <c r="V43" s="7">
+      <c r="X43" s="7">
         <v>2485.0940000000001</v>
       </c>
-      <c r="W43" s="7">
+      <c r="Y43" s="7">
         <v>2429.7310000000002</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z43" s="7">
+        <v>2452.6619999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>152</v>
       </c>
@@ -3724,17 +3890,20 @@
       <c r="P46" s="7">
         <v>28.94</v>
       </c>
-      <c r="U46" s="7">
+      <c r="W46" s="7">
         <v>298.209</v>
       </c>
-      <c r="V46" s="7">
+      <c r="X46" s="7">
         <v>195.43299999999999</v>
       </c>
-      <c r="W46" s="7">
+      <c r="Y46" s="7">
         <v>173.96100000000001</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z46" s="7">
+        <v>60.097999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>175</v>
       </c>
@@ -3747,17 +3916,20 @@
       <c r="P47" s="7">
         <v>74.489999999999995</v>
       </c>
-      <c r="U47" s="7">
+      <c r="W47" s="7">
         <v>127.119</v>
       </c>
-      <c r="V47" s="7">
+      <c r="X47" s="7">
         <v>132.9</v>
       </c>
-      <c r="W47" s="7">
+      <c r="Y47" s="7">
         <v>136.26499999999999</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z47" s="7">
+        <v>157.535</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>176</v>
       </c>
@@ -3767,17 +3939,20 @@
       <c r="P48" s="7">
         <v>6.4</v>
       </c>
-      <c r="U48" s="7">
+      <c r="W48" s="7">
         <v>12.92</v>
       </c>
-      <c r="V48" s="7">
+      <c r="X48" s="7">
         <v>12.829000000000001</v>
       </c>
-      <c r="W48" s="7">
+      <c r="Y48" s="7">
         <v>12.821999999999999</v>
       </c>
-    </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z48" s="7">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>177</v>
       </c>
@@ -3787,17 +3962,20 @@
       <c r="P49" s="7">
         <v>6.1619999999999999</v>
       </c>
-      <c r="U49" s="7">
+      <c r="W49" s="7">
         <v>12.775</v>
       </c>
-      <c r="V49" s="7">
+      <c r="X49" s="7">
         <v>12.829000000000001</v>
       </c>
-      <c r="W49" s="7">
+      <c r="Y49" s="7">
         <v>12.821999999999999</v>
       </c>
-    </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z49" s="7">
+        <v>10.574999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>178</v>
       </c>
@@ -3807,17 +3985,20 @@
       <c r="P50" s="7">
         <v>1.4019999999999999</v>
       </c>
-      <c r="U50" s="7">
+      <c r="W50" s="7">
         <v>6.9550000000000001</v>
       </c>
-      <c r="V50" s="7">
+      <c r="X50" s="7">
         <v>3.63</v>
       </c>
-      <c r="W50" s="7">
+      <c r="Y50" s="7">
         <v>4.8339999999999996</v>
       </c>
-    </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z50" s="7">
+        <v>3.282</v>
+      </c>
+    </row>
+    <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>179</v>
       </c>
@@ -3827,19 +4008,22 @@
       <c r="P51" s="7">
         <v>-0.187</v>
       </c>
-      <c r="U51" s="7">
+      <c r="W51" s="7">
         <v>-6.25</v>
       </c>
-      <c r="V51" s="7">
+      <c r="X51" s="7">
         <v>-5.556</v>
       </c>
-      <c r="W51" s="7">
+      <c r="Y51" s="7">
         <v>22.437000000000001</v>
       </c>
-    </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z51" s="7">
+        <v>33.372</v>
+      </c>
+    </row>
+    <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L52" s="7">
         <v>0.56499999999999995</v>
@@ -3847,17 +4031,20 @@
       <c r="P52" s="7">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="U52" s="7">
+      <c r="W52" s="7">
         <v>-11.65</v>
       </c>
-      <c r="V52" s="7">
+      <c r="X52" s="7">
         <v>4.7969999999999997</v>
       </c>
-      <c r="W52" s="7">
+      <c r="Y52" s="7">
         <v>-2.1760000000000002</v>
       </c>
-    </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z52" s="7">
+        <v>-15.308</v>
+      </c>
+    </row>
+    <row r="53" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>180</v>
       </c>
@@ -3867,17 +4054,20 @@
       <c r="P53" s="7">
         <v>-2.65</v>
       </c>
-      <c r="U53" s="7">
+      <c r="W53" s="7">
         <v>18.3</v>
       </c>
-      <c r="V53" s="7">
+      <c r="X53" s="7">
         <v>-19.100000000000001</v>
       </c>
-      <c r="W53" s="7">
+      <c r="Y53" s="7">
         <v>-90.25</v>
       </c>
-    </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z53" s="7">
+        <v>-2.65</v>
+      </c>
+    </row>
+    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>181</v>
       </c>
@@ -3887,17 +4077,20 @@
       <c r="P54" s="7">
         <v>0</v>
       </c>
-      <c r="U54" s="7">
+      <c r="W54" s="7">
         <v>0</v>
       </c>
-      <c r="V54" s="7">
+      <c r="X54" s="7">
         <v>-3.7389999999999999</v>
       </c>
-      <c r="W54" s="7">
+      <c r="Y54" s="7">
         <v>28.739000000000001</v>
       </c>
-    </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z54" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>182</v>
       </c>
@@ -3907,17 +4100,20 @@
       <c r="P55" s="7">
         <v>3.8660000000000001</v>
       </c>
-      <c r="U55" s="7">
+      <c r="W55" s="7">
         <v>-10.349</v>
       </c>
-      <c r="V55" s="7">
+      <c r="X55" s="7">
         <v>41.189</v>
       </c>
-      <c r="W55" s="7">
+      <c r="Y55" s="7">
         <v>45.499000000000002</v>
       </c>
-    </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z55" s="7">
+        <v>30.937999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>183</v>
       </c>
@@ -3927,17 +4123,20 @@
       <c r="P56" s="7">
         <v>9.7439999999999998</v>
       </c>
-      <c r="U56" s="7">
+      <c r="W56" s="7">
         <v>-0.41</v>
       </c>
-      <c r="V56" s="7">
+      <c r="X56" s="7">
         <v>2.5630000000000002</v>
       </c>
-      <c r="W56" s="7">
+      <c r="Y56" s="7">
         <v>-11.214</v>
       </c>
-    </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z56" s="7">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>184</v>
       </c>
@@ -3947,17 +4146,20 @@
       <c r="P57" s="7">
         <v>-0.32100000000000001</v>
       </c>
-      <c r="U57" s="7">
+      <c r="W57" s="7">
         <v>-2.9409999999999998</v>
       </c>
-      <c r="V57" s="7">
+      <c r="X57" s="7">
         <v>3.83</v>
       </c>
-      <c r="W57" s="7">
+      <c r="Y57" s="7">
         <v>-4.12</v>
       </c>
-    </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z57" s="7">
+        <v>-8.3439999999999994</v>
+      </c>
+    </row>
+    <row r="58" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>185</v>
       </c>
@@ -3967,17 +4169,20 @@
       <c r="P58" s="7">
         <v>9.31</v>
       </c>
-      <c r="U58" s="7">
+      <c r="W58" s="7">
         <v>-5.0490000000000004</v>
       </c>
-      <c r="V58" s="7">
+      <c r="X58" s="7">
         <v>-10.657</v>
       </c>
-      <c r="W58" s="7">
+      <c r="Y58" s="7">
         <v>-14.956</v>
       </c>
-    </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z58" s="7">
+        <v>-16.579000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>186</v>
       </c>
@@ -3987,17 +4192,20 @@
       <c r="P59" s="7">
         <v>-11.420999999999999</v>
       </c>
-      <c r="U59" s="7">
+      <c r="W59" s="7">
         <v>2.952</v>
       </c>
-      <c r="V59" s="7">
+      <c r="X59" s="7">
         <v>2.92</v>
       </c>
-      <c r="W59" s="7">
+      <c r="Y59" s="7">
         <v>-7.2050000000000001</v>
       </c>
-    </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z59" s="7">
+        <v>-11.019</v>
+      </c>
+    </row>
+    <row r="60" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>187</v>
       </c>
@@ -4007,17 +4215,20 @@
       <c r="P60" s="7">
         <v>-39.485999999999997</v>
       </c>
-      <c r="U60" s="7">
+      <c r="W60" s="7">
         <v>28.632000000000001</v>
       </c>
-      <c r="V60" s="7">
+      <c r="X60" s="7">
         <v>-10.260999999999999</v>
       </c>
-      <c r="W60" s="7">
+      <c r="Y60" s="7">
         <v>-21.039000000000001</v>
       </c>
-    </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z60" s="7">
+        <v>-36.244</v>
+      </c>
+    </row>
+    <row r="61" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>188</v>
       </c>
@@ -4029,22 +4240,26 @@
         <f>SUM(P46:P60)</f>
         <v>86.291000000000025</v>
       </c>
-      <c r="U61" s="7">
-        <f>SUM(U46:U60)</f>
-        <v>471.21300000000002</v>
-      </c>
-      <c r="V61" s="7">
-        <f>SUM(V46:V60)</f>
-        <v>363.60700000000003</v>
-      </c>
       <c r="W61" s="7">
         <f>SUM(W46:W60)</f>
+        <v>471.21300000000002</v>
+      </c>
+      <c r="X61" s="7">
+        <f>SUM(X46:X60)</f>
+        <v>363.60700000000003</v>
+      </c>
+      <c r="Y61" s="7">
+        <f>SUM(Y46:Y60)</f>
         <v>286.41900000000004</v>
       </c>
-    </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z61" s="7">
+        <f>SUM(Z46:Z60)</f>
+        <v>216.91599999999997</v>
+      </c>
+    </row>
+    <row r="63" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L63" s="7">
         <v>-104.90900000000001</v>
@@ -4052,17 +4267,20 @@
       <c r="P63" s="7">
         <v>-42.006999999999998</v>
       </c>
-      <c r="U63" s="7">
+      <c r="W63" s="7">
         <v>-148.22300000000001</v>
       </c>
-      <c r="V63" s="7">
+      <c r="X63" s="7">
         <v>-219.02099999999999</v>
       </c>
-      <c r="W63" s="7">
+      <c r="Y63" s="7">
         <v>-223.10300000000001</v>
       </c>
-    </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z63" s="7">
+        <v>-114.77500000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>189</v>
       </c>
@@ -4072,19 +4290,22 @@
       <c r="P64" s="7">
         <v>6.1420000000000003</v>
       </c>
-      <c r="U64" s="7">
+      <c r="W64" s="7">
         <v>19.690999999999999</v>
       </c>
-      <c r="V64" s="7">
+      <c r="X64" s="7">
         <v>7.7629999999999999</v>
       </c>
-      <c r="W64" s="7">
+      <c r="Y64" s="7">
         <v>15.372999999999999</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z64" s="7">
+        <v>34.47</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L65" s="7">
         <v>-5.2359999999999998</v>
@@ -4092,17 +4313,20 @@
       <c r="P65" s="7">
         <v>0</v>
       </c>
-      <c r="U65" s="7">
+      <c r="W65" s="7">
         <v>-182.352</v>
       </c>
-      <c r="V65" s="7">
+      <c r="X65" s="7">
         <v>-96.537000000000006</v>
       </c>
-      <c r="W65" s="7">
+      <c r="Y65" s="7">
         <v>-29.236000000000001</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z65" s="7">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>190</v>
       </c>
@@ -4112,17 +4336,20 @@
       <c r="P66" s="7">
         <v>5.2359999999999998</v>
       </c>
-      <c r="U66" s="7">
+      <c r="W66" s="7">
         <v>64.328999999999994</v>
       </c>
-      <c r="V66" s="7">
+      <c r="X66" s="7">
         <v>198.12</v>
       </c>
-      <c r="W66" s="7">
+      <c r="Y66" s="7">
         <v>66.584000000000003</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z66" s="7">
+        <v>29.236000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>191</v>
       </c>
@@ -4132,17 +4359,20 @@
       <c r="P67" s="7">
         <v>-6.2679999999999998</v>
       </c>
-      <c r="U67" s="7">
+      <c r="W67" s="7">
         <v>-17.282</v>
       </c>
-      <c r="V67" s="7">
+      <c r="X67" s="7">
         <v>-12.977</v>
       </c>
-      <c r="W67" s="7">
+      <c r="Y67" s="7">
         <v>-16.896999999999998</v>
       </c>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z67" s="7">
+        <v>-13.391</v>
+      </c>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>192</v>
       </c>
@@ -4154,19 +4384,23 @@
         <f>SUM(P63:P67)</f>
         <v>-36.896999999999991</v>
       </c>
-      <c r="U68" s="7">
-        <f>SUM(U63:U67)</f>
-        <v>-263.83699999999999</v>
-      </c>
-      <c r="V68" s="7">
-        <v>-21.709</v>
-      </c>
       <c r="W68" s="7">
         <f>SUM(W63:W67)</f>
+        <v>-263.83699999999999</v>
+      </c>
+      <c r="X68" s="7">
+        <v>-21.709</v>
+      </c>
+      <c r="Y68" s="7">
+        <f>SUM(Y63:Y67)</f>
         <v>-187.279</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z68" s="7">
+        <f>SUM(Z63:Z67)</f>
+        <v>-86.460000000000008</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>193</v>
       </c>
@@ -4176,17 +4410,20 @@
       <c r="P70" s="7">
         <v>25</v>
       </c>
-      <c r="U70" s="7">
+      <c r="W70" s="7">
         <v>58</v>
       </c>
-      <c r="V70" s="7">
+      <c r="X70" s="7">
         <v>0</v>
       </c>
-      <c r="W70" s="7">
+      <c r="Y70" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z70" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>194</v>
       </c>
@@ -4196,17 +4433,20 @@
       <c r="P71" s="7">
         <v>-35.526000000000003</v>
       </c>
-      <c r="U71" s="7">
+      <c r="W71" s="7">
         <v>-115.54</v>
       </c>
-      <c r="V71" s="7">
+      <c r="X71" s="7">
         <v>-69.180000000000007</v>
       </c>
-      <c r="W71" s="7">
+      <c r="Y71" s="7">
         <v>-120.518</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z71" s="7">
+        <v>-108.133</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>195</v>
       </c>
@@ -4216,17 +4456,20 @@
       <c r="P72" s="7">
         <v>-2.0209999999999999</v>
       </c>
-      <c r="U72" s="7">
+      <c r="W72" s="7">
         <v>8.3559999999999999</v>
       </c>
-      <c r="V72" s="7">
+      <c r="X72" s="7">
         <v>-14.101000000000001</v>
       </c>
-      <c r="W72" s="7">
+      <c r="Y72" s="7">
         <v>-3.504</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z72" s="7">
+        <v>-5.0679999999999996</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>196</v>
       </c>
@@ -4236,17 +4479,20 @@
       <c r="P73" s="7">
         <v>-1.9E-2</v>
       </c>
-      <c r="U73" s="7">
+      <c r="W73" s="7">
         <v>-0.95199999999999996</v>
       </c>
-      <c r="V73" s="7">
+      <c r="X73" s="7">
         <v>5.5E-2</v>
       </c>
-      <c r="W73" s="7">
+      <c r="Y73" s="7">
         <v>-6.2E-2</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z73" s="7">
+        <v>-0.85899999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>197</v>
       </c>
@@ -4256,17 +4502,20 @@
       <c r="P74" s="7">
         <v>-5.5430000000000001</v>
       </c>
-      <c r="U74" s="7">
+      <c r="W74" s="7">
         <v>-10.83</v>
       </c>
-      <c r="V74" s="7">
+      <c r="X74" s="7">
         <v>-11.542</v>
       </c>
-      <c r="W74" s="7">
+      <c r="Y74" s="7">
         <v>-11.295</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z74" s="7">
+        <v>-10.97</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>198</v>
       </c>
@@ -4276,17 +4525,20 @@
       <c r="P75" s="7">
         <v>-41.737000000000002</v>
       </c>
-      <c r="U75" s="7">
+      <c r="W75" s="7">
         <v>-65.001999999999995</v>
       </c>
-      <c r="V75" s="7">
+      <c r="X75" s="7">
         <v>-91.531000000000006</v>
       </c>
-      <c r="W75" s="7">
+      <c r="Y75" s="7">
         <v>-75.233000000000004</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z75" s="7">
+        <v>-75.566999999999993</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>199</v>
       </c>
@@ -4296,17 +4548,20 @@
       <c r="P76" s="7">
         <v>-1.9379999999999999</v>
       </c>
-      <c r="U76" s="7">
+      <c r="W76" s="7">
         <v>-16.222000000000001</v>
       </c>
-      <c r="V76" s="7">
+      <c r="X76" s="7">
         <v>-10.311</v>
       </c>
-      <c r="W76" s="7">
+      <c r="Y76" s="7">
         <v>-22.73</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z76" s="7">
+        <v>-2.0659999999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>200</v>
       </c>
@@ -4318,28 +4573,28 @@
         <f>SUM(P70:P76)</f>
         <v>-61.784000000000006</v>
       </c>
-      <c r="U77" s="7">
-        <f>SUM(U70:U76)+14.206</f>
-        <v>-127.98399999999999</v>
-      </c>
-      <c r="V77" s="7">
-        <f>SUM(V70:V76)+14.206</f>
-        <v>-182.40400000000002</v>
-      </c>
       <c r="W77" s="7">
         <f>SUM(W70:W76)+14.206</f>
-        <v>-219.136</v>
-      </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>201</v>
-      </c>
-    </row>
+        <v>-127.98399999999999</v>
+      </c>
+      <c r="X77" s="7">
+        <f>SUM(X70:X76)+14.206</f>
+        <v>-182.40400000000002</v>
+      </c>
+      <c r="Y77" s="7">
+        <f>SUM(Y70:Y76)</f>
+        <v>-233.34199999999998</v>
+      </c>
+      <c r="Z77" s="7">
+        <f>SUM(Z70:Z76)</f>
+        <v>-177.66299999999998</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="X11:AH11" formula="1"/>
+    <ignoredError sqref="AA11:AJ11" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
